--- a/artfynd/A 17481-2026 artfynd.xlsx
+++ b/artfynd/A 17481-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5207,6 +5207,648 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132799480</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92208</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>658</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>438029</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7009973</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132801561</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>437918</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7010065</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132799635</v>
+      </c>
+      <c r="B45" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>438022</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7009994</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132799502</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>438029</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7009973</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132801551</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>437918</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7010065</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132798197</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>437977</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7009858</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17481-2026 artfynd.xlsx
+++ b/artfynd/A 17481-2026 artfynd.xlsx
@@ -5212,7 +5212,7 @@
         <v>132799480</v>
       </c>
       <c r="B43" t="n">
-        <v>92208</v>
+        <v>92209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>132801561</v>
       </c>
       <c r="B44" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>132799635</v>
       </c>
       <c r="B45" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>132799502</v>
       </c>
       <c r="B46" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5640,7 +5640,7 @@
         <v>132801551</v>
       </c>
       <c r="B47" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>132798197</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 17481-2026 artfynd.xlsx
+++ b/artfynd/A 17481-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89596061</v>
+        <v>89596049</v>
       </c>
       <c r="B2" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438147.1113018537</v>
+        <v>438073</v>
       </c>
       <c r="R2" t="n">
-        <v>7010689.879124686</v>
+        <v>7010757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89596057</v>
+        <v>89596069</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438148.9606549114</v>
+        <v>438074</v>
       </c>
       <c r="R3" t="n">
-        <v>7010692.099061659</v>
+        <v>7010758</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89596043</v>
+        <v>122773591</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,34 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438352.7905881174</v>
+        <v>438161</v>
       </c>
       <c r="R4" t="n">
-        <v>7010698.120921676</v>
+        <v>7010308</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,27 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,31 +962,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89596054</v>
+        <v>122773592</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,34 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438098.1005549211</v>
+        <v>438283</v>
       </c>
       <c r="R5" t="n">
-        <v>7010725.101157578</v>
+        <v>7010189</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,22 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,53 +1059,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89596046</v>
+        <v>89596050</v>
       </c>
       <c r="B6" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438209.0636698382</v>
+        <v>438211</v>
       </c>
       <c r="R6" t="n">
-        <v>7010717.109672974</v>
+        <v>7010748</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1139,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,15 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89596050</v>
+        <v>89596057</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1300,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438211.0142279203</v>
+        <v>438149</v>
       </c>
       <c r="R7" t="n">
-        <v>7010748.196368557</v>
+        <v>7010692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1240,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,50 +1273,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89596071</v>
+        <v>122773626</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438209.9667237623</v>
+        <v>438169</v>
       </c>
       <c r="R8" t="n">
-        <v>7010717.092374323</v>
+        <v>7010796</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,22 +1338,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,53 +1363,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89596068</v>
+        <v>89596071</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438112.793286343</v>
+        <v>438210</v>
       </c>
       <c r="R9" t="n">
-        <v>7010713.993414507</v>
+        <v>7010717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,19 +1443,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,50 +1476,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773619</v>
+        <v>89596061</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438283</v>
+        <v>438147</v>
       </c>
       <c r="R10" t="n">
-        <v>7010189</v>
+        <v>7010690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,17 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,44 +1561,43 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773601</v>
+        <v>122773625</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1748,17 +1605,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438600</v>
+        <v>438106</v>
       </c>
       <c r="R11" t="n">
-        <v>7010330</v>
+        <v>7010492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1664,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackande/trummande</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,15 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122773592</v>
+        <v>89596043</v>
       </c>
       <c r="B12" t="n">
-        <v>90963</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,34 +1702,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438283</v>
+        <v>438353</v>
       </c>
       <c r="R12" t="n">
-        <v>7010189</v>
+        <v>7010698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,12 +1756,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,27 +1781,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122773615</v>
+        <v>122773595</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,10 +1832,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438145</v>
+        <v>438193</v>
       </c>
       <c r="R13" t="n">
-        <v>7010332</v>
+        <v>7010800</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2031,15 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122773599</v>
+        <v>122773596</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2071,10 +1934,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438431</v>
+        <v>438245</v>
       </c>
       <c r="R14" t="n">
-        <v>7010633</v>
+        <v>7010805</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +1974,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,15 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122773626</v>
+        <v>122773597</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,21 +2012,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2178,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438169</v>
+        <v>438355</v>
       </c>
       <c r="R15" t="n">
-        <v>7010796</v>
+        <v>7010686</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2218,7 +2076,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122773614</v>
+        <v>122773598</v>
       </c>
       <c r="B16" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2285,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438145</v>
+        <v>438360</v>
       </c>
       <c r="R16" t="n">
-        <v>7010359</v>
+        <v>7010674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2352,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122773617</v>
+        <v>122773599</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,10 +2240,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438166</v>
+        <v>438431</v>
       </c>
       <c r="R17" t="n">
-        <v>7010295</v>
+        <v>7010633</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,7 +2280,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2459,15 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122773618</v>
+        <v>122773600</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2499,10 +2342,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438180</v>
+        <v>438630</v>
       </c>
       <c r="R18" t="n">
-        <v>7010258</v>
+        <v>7010427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2539,7 +2382,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2566,15 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122773598</v>
+        <v>122773601</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,10 +2444,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438360</v>
+        <v>438600</v>
       </c>
       <c r="R19" t="n">
-        <v>7010674</v>
+        <v>7010330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,15 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122773624</v>
+        <v>122773602</v>
       </c>
       <c r="B20" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,46 +2522,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438215</v>
+        <v>438601</v>
       </c>
       <c r="R20" t="n">
-        <v>7010784</v>
+        <v>7010314</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2765,7 +2586,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 6 st</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2792,15 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122773595</v>
+        <v>122773603</v>
       </c>
       <c r="B21" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2832,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438193</v>
+        <v>438601</v>
       </c>
       <c r="R21" t="n">
-        <v>7010800</v>
+        <v>7010302</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2872,7 +2688,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2899,15 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122773610</v>
+        <v>122773604</v>
       </c>
       <c r="B22" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438054</v>
+        <v>438531</v>
       </c>
       <c r="R22" t="n">
-        <v>7010615</v>
+        <v>7010323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3006,15 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122773616</v>
+        <v>122773605</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3046,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438161</v>
+        <v>438538</v>
       </c>
       <c r="R23" t="n">
-        <v>7010308</v>
+        <v>7010447</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3086,7 +2892,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,15 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122773597</v>
+        <v>122773606</v>
       </c>
       <c r="B24" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,17 +2947,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438355</v>
+        <v>438521</v>
       </c>
       <c r="R24" t="n">
-        <v>7010686</v>
+        <v>7010477</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3193,7 +3014,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3220,15 +3041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122773625</v>
+        <v>122773607</v>
       </c>
       <c r="B25" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,16 +3052,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3253,29 +3069,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>438106</v>
+        <v>438336</v>
       </c>
       <c r="R25" t="n">
-        <v>7010492</v>
+        <v>7010625</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3312,7 +3116,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Hackande/trummande</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,15 +3143,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122773600</v>
+        <v>122773609</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3379,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438630</v>
+        <v>438318</v>
       </c>
       <c r="R26" t="n">
-        <v>7010427</v>
+        <v>7010644</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3419,7 +3218,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,15 +3245,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122773607</v>
+        <v>122773610</v>
       </c>
       <c r="B27" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,10 +3280,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438336</v>
+        <v>438054</v>
       </c>
       <c r="R27" t="n">
-        <v>7010625</v>
+        <v>7010615</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3556,12 +3350,7 @@
         <v>122773611</v>
       </c>
       <c r="B28" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,15 +3449,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122773609</v>
+        <v>122773612</v>
       </c>
       <c r="B29" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3700,10 +3484,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438318</v>
+        <v>438085</v>
       </c>
       <c r="R29" t="n">
-        <v>7010644</v>
+        <v>7010568</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,7 +3524,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3767,15 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122773591</v>
+        <v>122773613</v>
       </c>
       <c r="B30" t="n">
-        <v>90963</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3783,21 +3562,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3807,10 +3586,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438161</v>
+        <v>438083</v>
       </c>
       <c r="R30" t="n">
-        <v>7010308</v>
+        <v>7010509</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3843,6 +3622,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3869,15 +3653,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122773604</v>
+        <v>122773614</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3909,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438531</v>
+        <v>438145</v>
       </c>
       <c r="R31" t="n">
-        <v>7010323</v>
+        <v>7010359</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3976,15 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122773602</v>
+        <v>122773615</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4016,10 +3790,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438601</v>
+        <v>438145</v>
       </c>
       <c r="R32" t="n">
-        <v>7010314</v>
+        <v>7010332</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4056,7 +3830,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4083,15 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122773596</v>
+        <v>122773616</v>
       </c>
       <c r="B33" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4123,10 +3892,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438245</v>
+        <v>438161</v>
       </c>
       <c r="R33" t="n">
-        <v>7010805</v>
+        <v>7010308</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4163,7 +3932,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4190,15 +3959,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122773605</v>
+        <v>122773617</v>
       </c>
       <c r="B34" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4230,10 +3994,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438538</v>
+        <v>438166</v>
       </c>
       <c r="R34" t="n">
-        <v>7010447</v>
+        <v>7010295</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4270,7 +4034,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4297,15 +4061,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122773613</v>
+        <v>122773618</v>
       </c>
       <c r="B35" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4337,10 +4096,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438083</v>
+        <v>438180</v>
       </c>
       <c r="R35" t="n">
-        <v>7010509</v>
+        <v>7010258</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4377,7 +4136,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4404,15 +4163,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122773612</v>
+        <v>122773619</v>
       </c>
       <c r="B36" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4444,10 +4198,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438085</v>
+        <v>438283</v>
       </c>
       <c r="R36" t="n">
-        <v>7010568</v>
+        <v>7010189</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4484,7 +4238,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4511,15 +4265,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122797613</v>
+        <v>122797611</v>
       </c>
       <c r="B37" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4551,10 +4300,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438189</v>
+        <v>438177</v>
       </c>
       <c r="R37" t="n">
-        <v>7010284</v>
+        <v>7010646</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4591,7 +4340,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4618,10 +4367,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122773606</v>
+        <v>122797612</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4646,37 +4395,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438521</v>
+        <v>438247</v>
       </c>
       <c r="R38" t="n">
-        <v>7010477</v>
+        <v>7010584</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4703,17 +4432,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Födosökte på flertalet träd och trummade. Hörde ev ytterligare en tretå i närheten samtidigt.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4740,15 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>89600497</v>
+        <v>122797613</v>
       </c>
       <c r="B39" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4756,34 +4480,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438057.1641163478</v>
+        <v>438189</v>
       </c>
       <c r="R39" t="n">
-        <v>7010027.998462055</v>
+        <v>7010284</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4810,22 +4534,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4836,40 +4555,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Allmän</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89600500</v>
+        <v>89596054</v>
       </c>
       <c r="B40" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4877,21 +4582,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2809</v>
+        <v>102612</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4901,10 +4606,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438057.1641163478</v>
+        <v>438098</v>
       </c>
       <c r="R40" t="n">
-        <v>7010027.998462055</v>
+        <v>7010725</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4934,19 +4639,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4977,15 +4672,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>89600502</v>
+        <v>122773624</v>
       </c>
       <c r="B41" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4993,34 +4683,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>437791.8373623165</v>
+        <v>438215</v>
       </c>
       <c r="R41" t="n">
-        <v>7010115.215570992</v>
+        <v>7010784</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5047,22 +4749,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Minst 6 st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5077,31 +4774,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>89600493</v>
+        <v>89596039</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5109,21 +4797,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5133,10 +4821,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438057.1641163478</v>
+        <v>438334</v>
       </c>
       <c r="R42" t="n">
-        <v>7010027.998462055</v>
+        <v>7010657</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5166,19 +4854,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5209,10 +4887,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132799480</v>
+        <v>89596055</v>
       </c>
       <c r="B43" t="n">
-        <v>92217</v>
+        <v>58057</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5220,34 +4898,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>103031</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438029</v>
+        <v>438201</v>
       </c>
       <c r="R43" t="n">
-        <v>7009973</v>
+        <v>7010707</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5274,22 +4952,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5304,60 +4972,64 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132801561</v>
+        <v>89596046</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>80392</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>437918</v>
+        <v>438209</v>
       </c>
       <c r="R44" t="n">
-        <v>7010065</v>
+        <v>7010717</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5381,22 +5053,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5411,60 +5073,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132799635</v>
+        <v>133454044</v>
       </c>
       <c r="B45" t="n">
-        <v>83315</v>
+        <v>92201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>67</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>438022</v>
+        <v>437630</v>
       </c>
       <c r="R45" t="n">
-        <v>7009994</v>
+        <v>7009596</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5488,22 +5154,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5518,57 +5174,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132799502</v>
+        <v>133454045</v>
       </c>
       <c r="B46" t="n">
-        <v>91918</v>
+        <v>92201</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>438029</v>
+        <v>437878</v>
       </c>
       <c r="R46" t="n">
-        <v>7009973</v>
+        <v>7010079</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5595,22 +5251,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5625,22 +5271,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>132801551</v>
+        <v>132341099</v>
       </c>
       <c r="B47" t="n">
-        <v>83315</v>
+        <v>92245</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5648,37 +5294,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>437918</v>
+        <v>437567</v>
       </c>
       <c r="R47" t="n">
-        <v>7010065</v>
+        <v>7010357</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5702,22 +5348,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5732,22 +5368,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>132798197</v>
+        <v>133454050</v>
       </c>
       <c r="B48" t="n">
-        <v>79333</v>
+        <v>92245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5755,37 +5391,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>437977</v>
+        <v>437672</v>
       </c>
       <c r="R48" t="n">
-        <v>7009858</v>
+        <v>7009651</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5809,22 +5445,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>12:39</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5839,22 +5465,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>132946942</v>
+        <v>133454051</v>
       </c>
       <c r="B49" t="n">
-        <v>57136</v>
+        <v>92245</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5862,42 +5488,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Mattmar, Slåttmyrtjärnarna, Mattmar, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438000</v>
+        <v>437618</v>
       </c>
       <c r="R49" t="n">
-        <v>7009861</v>
+        <v>7009600</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5921,22 +5542,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>12:48</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5951,22 +5562,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>132946772</v>
+        <v>133454052</v>
       </c>
       <c r="B50" t="n">
-        <v>91942</v>
+        <v>92245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,37 +5585,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438002</v>
+        <v>437747</v>
       </c>
       <c r="R50" t="n">
-        <v>7009985</v>
+        <v>7009664</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6028,22 +5639,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6058,22 +5659,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>132946683</v>
+        <v>133454056</v>
       </c>
       <c r="B51" t="n">
-        <v>91924</v>
+        <v>91970</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6101,17 +5702,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>437974</v>
+        <v>437754</v>
       </c>
       <c r="R51" t="n">
-        <v>7009986</v>
+        <v>7009785</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6135,22 +5736,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6165,22 +5756,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>132946900</v>
+        <v>133453991</v>
       </c>
       <c r="B52" t="n">
-        <v>57136</v>
+        <v>91974</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6188,42 +5779,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Mattmar, Slåttmyrtjärnarna, Mattmar, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>437974</v>
+        <v>437676</v>
       </c>
       <c r="R52" t="n">
-        <v>7009986</v>
+        <v>7009676</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6247,22 +5833,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6277,22 +5853,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>132946658</v>
+        <v>133453992</v>
       </c>
       <c r="B53" t="n">
-        <v>83183</v>
+        <v>91974</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6300,37 +5876,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+          <t>Sällsjön Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438058</v>
+        <v>437673</v>
       </c>
       <c r="R53" t="n">
-        <v>7009953</v>
+        <v>7009652</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6354,22 +5930,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6384,44 +5950,44 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Matilda Pettersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133453997</v>
+        <v>133453993</v>
       </c>
       <c r="B54" t="n">
-        <v>92184</v>
+        <v>91974</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6431,10 +5997,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>437962</v>
+        <v>437648</v>
       </c>
       <c r="R54" t="n">
-        <v>7009949</v>
+        <v>7009626</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6493,10 +6059,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133454056</v>
+        <v>133453994</v>
       </c>
       <c r="B55" t="n">
-        <v>91955</v>
+        <v>91974</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6504,21 +6070,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6528,10 +6094,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>437754</v>
+        <v>437655</v>
       </c>
       <c r="R55" t="n">
-        <v>7009785</v>
+        <v>7009585</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6590,10 +6156,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133454045</v>
+        <v>133453989</v>
       </c>
       <c r="B56" t="n">
-        <v>92186</v>
+        <v>92318</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6601,21 +6167,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>67</v>
+        <v>2062</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6625,10 +6191,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>437878</v>
+        <v>437654</v>
       </c>
       <c r="R56" t="n">
-        <v>7010079</v>
+        <v>7009586</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6667,8 +6233,9 @@
         <v>0</v>
       </c>
       <c r="AE56" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6687,32 +6254,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133454057</v>
+        <v>132340934</v>
       </c>
       <c r="B57" t="n">
-        <v>91955</v>
+        <v>91937</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6722,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>437982</v>
+        <v>437567</v>
       </c>
       <c r="R57" t="n">
-        <v>7010013</v>
+        <v>7010358</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6752,12 +6319,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6784,48 +6351,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133453995</v>
+        <v>132801561</v>
       </c>
       <c r="B58" t="n">
-        <v>91959</v>
+        <v>79373</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438026</v>
+        <v>437918</v>
       </c>
       <c r="R58" t="n">
-        <v>7010005</v>
+        <v>7010065</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6849,12 +6416,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6869,22 +6446,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133454019</v>
+        <v>132801551</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>83358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6892,37 +6469,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>437748</v>
+        <v>437918</v>
       </c>
       <c r="R59" t="n">
-        <v>7009847</v>
+        <v>7010065</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6946,17 +6523,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6971,39 +6553,39 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133454020</v>
+        <v>133454046</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7018,10 +6600,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>437737</v>
+        <v>437622</v>
       </c>
       <c r="R60" t="n">
-        <v>7009749</v>
+        <v>7009602</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7058,7 +6640,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7085,32 +6667,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133454051</v>
+        <v>133454047</v>
       </c>
       <c r="B61" t="n">
-        <v>92230</v>
+        <v>57972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7120,10 +6702,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>437618</v>
+        <v>437636</v>
       </c>
       <c r="R61" t="n">
-        <v>7009600</v>
+        <v>7009579</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7156,6 +6738,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7182,32 +6769,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133453991</v>
+        <v>133454049</v>
       </c>
       <c r="B62" t="n">
-        <v>91959</v>
+        <v>57972</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7217,10 +6804,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>437676</v>
+        <v>437709</v>
       </c>
       <c r="R62" t="n">
-        <v>7009676</v>
+        <v>7009644</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7253,6 +6840,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7279,45 +6871,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133454044</v>
+        <v>89600502</v>
       </c>
       <c r="B63" t="n">
-        <v>92186</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>437630</v>
+        <v>437792</v>
       </c>
       <c r="R63" t="n">
-        <v>7009596</v>
+        <v>7010115</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7344,12 +6936,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7364,44 +6956,48 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133453989</v>
+        <v>133454019</v>
       </c>
       <c r="B64" t="n">
-        <v>92303</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7411,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>437654</v>
+        <v>437748</v>
       </c>
       <c r="R64" t="n">
-        <v>7009586</v>
+        <v>7009847</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7449,13 +7045,17 @@
           <t>2026-05-13</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF64" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7474,7 +7074,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133454027</v>
+        <v>133454020</v>
       </c>
       <c r="B65" t="n">
         <v>57975</v>
@@ -7509,10 +7109,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438045</v>
+        <v>437737</v>
       </c>
       <c r="R65" t="n">
-        <v>7010081</v>
+        <v>7009749</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7549,7 +7149,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7576,10 +7176,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133453992</v>
+        <v>133454021</v>
       </c>
       <c r="B66" t="n">
-        <v>91959</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7587,21 +7187,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7611,10 +7211,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>437673</v>
+        <v>437845</v>
       </c>
       <c r="R66" t="n">
-        <v>7009652</v>
+        <v>7009894</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7647,6 +7247,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7673,10 +7278,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133454049</v>
+        <v>133454023</v>
       </c>
       <c r="B67" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,16 +7289,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7708,10 +7313,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>437709</v>
+        <v>437853</v>
       </c>
       <c r="R67" t="n">
-        <v>7009644</v>
+        <v>7009903</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7748,7 +7353,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7775,10 +7380,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133454042</v>
+        <v>133454024</v>
       </c>
       <c r="B68" t="n">
-        <v>91909</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7786,21 +7391,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7810,10 +7415,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>437984</v>
+        <v>437906</v>
       </c>
       <c r="R68" t="n">
-        <v>7009997</v>
+        <v>7009917</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7846,6 +7451,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7872,32 +7482,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133454029</v>
+        <v>133454054</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7907,10 +7517,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>437932</v>
+        <v>437734</v>
       </c>
       <c r="R69" t="n">
-        <v>7009993</v>
+        <v>7009703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7947,7 +7557,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack (års)färska och äldre</t>
+          <t>Minst 150</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7974,10 +7584,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133454025</v>
+        <v>133454042</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>91924</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7985,21 +7595,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>112</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8009,10 +7619,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438077</v>
+        <v>437984</v>
       </c>
       <c r="R70" t="n">
-        <v>7010083</v>
+        <v>7009997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8045,11 +7655,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8076,10 +7681,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133454050</v>
+        <v>132799480</v>
       </c>
       <c r="B71" t="n">
-        <v>92230</v>
+        <v>92245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8107,14 +7712,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>437672</v>
+        <v>438029</v>
       </c>
       <c r="R71" t="n">
-        <v>7009651</v>
+        <v>7009973</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8141,12 +7746,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8161,22 +7776,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133454031</v>
+        <v>133454053</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>92245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8184,21 +7799,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8208,10 +7823,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>437923</v>
+        <v>438010</v>
       </c>
       <c r="R72" t="n">
-        <v>7009988</v>
+        <v>7010094</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8244,11 +7859,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack (års)färska och äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8275,10 +7885,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133454047</v>
+        <v>132946683</v>
       </c>
       <c r="B73" t="n">
-        <v>57972</v>
+        <v>91970</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8286,37 +7896,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>437636</v>
+        <v>437974</v>
       </c>
       <c r="R73" t="n">
-        <v>7009579</v>
+        <v>7009986</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8340,17 +7950,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8365,22 +7980,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133453993</v>
+        <v>133454057</v>
       </c>
       <c r="B74" t="n">
-        <v>91959</v>
+        <v>91970</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8388,21 +8003,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8412,10 +8027,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>437648</v>
+        <v>437982</v>
       </c>
       <c r="R74" t="n">
-        <v>7009626</v>
+        <v>7010013</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8474,10 +8089,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133454023</v>
+        <v>89600493</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>91909</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8485,34 +8100,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>437853</v>
+        <v>438057</v>
       </c>
       <c r="R75" t="n">
-        <v>7009903</v>
+        <v>7010028</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8539,17 +8154,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8564,22 +8174,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133454021</v>
+        <v>132799502</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8587,34 +8201,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>437845</v>
+        <v>438029</v>
       </c>
       <c r="R76" t="n">
-        <v>7009894</v>
+        <v>7009973</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8641,17 +8255,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8666,22 +8285,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133453996</v>
+        <v>133453995</v>
       </c>
       <c r="B77" t="n">
-        <v>91959</v>
+        <v>91974</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8713,10 +8332,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>438011</v>
+        <v>438026</v>
       </c>
       <c r="R77" t="n">
-        <v>7010091</v>
+        <v>7010005</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8775,10 +8394,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133454053</v>
+        <v>133453996</v>
       </c>
       <c r="B78" t="n">
-        <v>92230</v>
+        <v>91974</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8786,21 +8405,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8810,10 +8429,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>438010</v>
+        <v>438011</v>
       </c>
       <c r="R78" t="n">
-        <v>7010094</v>
+        <v>7010091</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8872,10 +8491,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133454054</v>
+        <v>132946772</v>
       </c>
       <c r="B79" t="n">
-        <v>99180</v>
+        <v>91988</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8883,37 +8502,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>437734</v>
+        <v>438002</v>
       </c>
       <c r="R79" t="n">
-        <v>7009703</v>
+        <v>7009985</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8937,17 +8556,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 150</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8962,22 +8586,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133454052</v>
+        <v>132946658</v>
       </c>
       <c r="B80" t="n">
-        <v>92230</v>
+        <v>83222</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8985,37 +8609,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>437747</v>
+        <v>438058</v>
       </c>
       <c r="R80" t="n">
-        <v>7009664</v>
+        <v>7009953</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9039,12 +8663,22 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9059,57 +8693,57 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133454046</v>
+        <v>89600500</v>
       </c>
       <c r="B81" t="n">
-        <v>57972</v>
+        <v>96338</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>2809</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>437622</v>
+        <v>438057</v>
       </c>
       <c r="R81" t="n">
-        <v>7009602</v>
+        <v>7010028</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9136,17 +8770,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9161,44 +8790,48 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133454028</v>
+        <v>133453997</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>92199</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9208,10 +8841,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>437970</v>
+        <v>437962</v>
       </c>
       <c r="R82" t="n">
-        <v>7010113</v>
+        <v>7009949</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9244,11 +8877,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack (års) färska och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9275,45 +8903,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133454024</v>
+        <v>89600497</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Baksjöhallen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>437906</v>
+        <v>438057</v>
       </c>
       <c r="R83" t="n">
-        <v>7009917</v>
+        <v>7010028</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9340,17 +8968,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2020-09-24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2020-09-25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9361,64 +8984,73 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Allmän</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133453994</v>
+        <v>132798197</v>
       </c>
       <c r="B84" t="n">
-        <v>91959</v>
+        <v>79373</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sällsjön Ö, Jmt</t>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>437655</v>
+        <v>437977</v>
       </c>
       <c r="R84" t="n">
-        <v>7009585</v>
+        <v>7009858</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9442,12 +9074,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9462,15 +9104,1058 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>132799635</v>
+      </c>
+      <c r="B85" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>438022</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7009994</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>133454025</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>438077</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7010083</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>133454027</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>438045</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7010081</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>133454028</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>437970</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7010113</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack (års) färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>133454029</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>437932</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7009993</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack (års)färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>133454031</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sällsjön Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>437923</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7009988</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack (års)färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89600487</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Baksjöhallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>438059</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7010031</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>132946900</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Mattmar, Slåttmyrtjärnarna, Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>437974</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7009986</v>
+      </c>
+      <c r="S92" t="n">
+        <v>50</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132946942</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57153</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Mattmar, Slåttmyrtjärnarna, Mattmar, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>438000</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7009861</v>
+      </c>
+      <c r="S93" t="n">
+        <v>20</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>89600494</v>
+      </c>
+      <c r="B94" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Baksjöhallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>438057</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7010028</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2020-09-24</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2020-09-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17481-2026 artfynd.xlsx
+++ b/artfynd/A 17481-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596049</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773592</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596050</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596057</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773626</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596071</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596061</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1688,6 +1738,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596043</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773595</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773596</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773597</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773598</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773599</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773600</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773601</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773602</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773603</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773604</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773605</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3038,6 +3153,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773606</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3140,6 +3260,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773607</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773609</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3344,6 +3474,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773610</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3446,6 +3581,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773611</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3548,6 +3688,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773612</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3650,6 +3795,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773613</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773614</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3854,6 +4009,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773615</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3956,6 +4116,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773616</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4058,6 +4223,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773617</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4160,6 +4330,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773618</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4262,6 +4437,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773619</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4364,6 +4544,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797611</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4466,6 +4651,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797612</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4568,6 +4758,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797613</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4669,6 +4864,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596054</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4783,6 +4983,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773624</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4884,6 +5089,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596039</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4985,6 +5195,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596055</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5086,6 +5301,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89596046</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5183,6 +5403,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454044</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5280,6 +5505,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454045</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5377,6 +5607,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5474,6 +5709,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132341099</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5581,6 +5821,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799480</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5678,6 +5923,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5775,6 +6025,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454051</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5872,6 +6127,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454052</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5969,6 +6229,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454053</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6076,6 +6341,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132946683</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6173,6 +6443,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454056</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6270,6 +6545,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454057</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6371,6 +6651,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600493</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6478,6 +6763,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799502</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6575,6 +6865,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453991</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6672,6 +6967,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453992</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6769,6 +7069,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453993</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6866,6 +7171,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453994</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6963,6 +7273,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453995</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7060,6 +7375,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453996</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7167,6 +7487,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132946772</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7274,6 +7599,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132946658</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7372,6 +7702,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453989</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7473,6 +7808,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600500</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7570,6 +7910,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133453997</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7667,6 +8012,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132340934</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7773,6 +8123,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600497</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7880,6 +8235,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132798197</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7987,6 +8347,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132801561</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8094,6 +8459,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799635</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8201,6 +8571,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132801551</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8303,6 +8678,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454046</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8405,6 +8785,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454047</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8507,6 +8892,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454049</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8608,6 +8998,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600502</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8710,6 +9105,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454019</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8812,6 +9212,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454020</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8914,6 +9319,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454021</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9016,6 +9426,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454023</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9118,6 +9533,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454024</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9220,6 +9640,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454025</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9322,6 +9747,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454027</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9424,6 +9854,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454028</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9526,6 +9961,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454029</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9628,6 +10068,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454031</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9729,6 +10174,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600487</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9841,6 +10291,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132946900</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9953,6 +10408,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132946942</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10054,6 +10514,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600494</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10156,8 +10621,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133454054</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>